--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1264,7 +1264,7 @@
     <t>outboundRelationship[typeCode=COMP].target</t>
   </si>
   <si>
-    <t>++: reference from null (#null)</t>
+    <t>++: reference</t>
   </si>
   <si>
     <t>DiagnosticReport.imagingStudy</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA EM (file 63.02) to FHIR DiagnosticReport</t>
+    <t>This StructureDefinition contains the maps for VistA file EM (#63.02) to LabObservationDiagnosticReport</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$43</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="415">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Lab Observation: Electron Microscopy {DiagnosticReport}</t>
+    <t>Lab Observation: Electron Microscopy DiagnosticReport</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file EM (#63.02) to LabObservationDiagnosticReport</t>
+    <t>This StructureDefinition contains the maps for VistA file EM (#63.02) to us-core-diagnosticreport-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/StructureDefinition/LabObservationDiagnosticReport</t>
+    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-diagnosticreport-lab</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -821,74 +821,6 @@
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-2:1419: fixed value = http://terminology.hl7.org/CodeSystem/v2-0074|LAB {null}</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>1419: fixed value = http://terminology.hl7.org/CodeSystem/v2-0074|LAB</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (#60-64 &gt; 64-13 &gt; 64.21-.01)</t>
   </si>
   <si>
     <t>DiagnosticReport.category:LaboratorySlice</t>
@@ -969,30 +901,6 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
-  </si>
-  <si>
-    <t>Micro.AntibioticSensitivity.LRDFN
-Micro.AntibioticSensitivityComment.LRDFN
-Pathology.Autopsy.LRDFN
-Micro.BacteriologyReports.LRDFN
-Pathology.CytoOrganTissueFunction.StaffIEN
-Micro.MicroAntibioticLevel.LRDFN
-Micro.MicroAudit.LRDFN
-Micro.Microbiology.LRDFN
-Micro.MicroOrderedTest.LRDFN
-Micro.MicroSterilityResults.LRDFN
-Micro.MycobacteriologyReports.LRDFN
-Micro.Mycology.LRDFN
-Micro.MycologyReports.LRDFN
-Micro.Parasitology.LRDFN
-Micro.ParasitologyReports.LRDFN
-Micro.ParasitologyStage.LRDFN
-SStaff.SMicroOrderedTest.LRDFN
-Micro.Virology.LRDFN
-Micro.VirologyReports.LRDFN</t>
   </si>
   <si>
     <t>DiagnosticReport.encounter</t>
@@ -1748,7 +1656,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP47"/>
+  <dimension ref="A1:AP43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.51953125" customWidth="true" bestFit="true"/>
@@ -1790,7 +1698,7 @@
     <col min="38" max="38" width="171.66796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="121.93359375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="165.01953125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="133.390625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="61.08203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -3747,7 +3655,7 @@
         <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>82</v>
@@ -4449,38 +4357,42 @@
         <v>259</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>161</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4490,7 +4402,7 @@
         <v>82</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>82</v>
@@ -4505,13 +4417,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -4529,31 +4441,31 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>163</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>164</v>
+        <v>257</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -4564,42 +4476,42 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>136</v>
+        <v>263</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>138</v>
+        <v>264</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>166</v>
+        <v>265</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>140</v>
+        <v>266</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4625,55 +4537,55 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>170</v>
+        <v>262</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>82</v>
+        <v>272</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -4684,24 +4596,24 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>274</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>82</v>
@@ -4710,19 +4622,17 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4771,34 +4681,34 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>268</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4806,14 +4716,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4832,19 +4742,19 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>160</v>
+        <v>285</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4893,7 +4803,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4908,19 +4818,19 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -4928,20 +4838,18 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>248</v>
+        <v>295</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>91</v>
@@ -4956,18 +4864,20 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>182</v>
+        <v>296</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>297</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
+        <v>298</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -4976,7 +4886,7 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>82</v>
@@ -4991,55 +4901,53 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>256</v>
+        <v>304</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>258</v>
+        <v>306</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5050,18 +4958,20 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="D28" t="s" s="2">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>91</v>
@@ -5076,18 +4986,20 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>182</v>
+        <v>309</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5111,13 +5023,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5135,53 +5047,53 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>91</v>
@@ -5196,17 +5108,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="O29" t="s" s="2">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5255,7 +5169,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5264,50 +5178,50 @@
         <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>306</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
@@ -5316,19 +5230,19 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5377,13 +5291,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5392,44 +5306,44 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -5438,19 +5352,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5487,41 +5401,43 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5532,47 +5448,45 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>323</v>
+        <v>349</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5621,56 +5535,56 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>345</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>329</v>
+        <v>281</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>92</v>
@@ -5679,22 +5593,22 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5743,16 +5657,16 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>103</v>
@@ -5761,31 +5675,31 @@
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5795,29 +5709,27 @@
         <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -5865,7 +5777,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5880,34 +5792,34 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5926,19 +5838,17 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -5987,7 +5897,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6002,16 +5912,16 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6022,10 +5932,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6036,7 +5946,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6048,20 +5958,16 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>370</v>
+        <v>160</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>371</v>
+        <v>161</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6109,28 +6015,28 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>369</v>
+        <v>163</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>303</v>
+        <v>164</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
@@ -6151,7 +6057,7 @@
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>377</v>
+        <v>136</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6161,7 +6067,7 @@
         <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6170,20 +6076,18 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>378</v>
+        <v>137</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>379</v>
+        <v>138</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>380</v>
+        <v>166</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6231,7 +6135,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>376</v>
+        <v>170</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6243,22 +6147,22 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>384</v>
+        <v>164</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6266,14 +6170,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6286,24 +6190,26 @@
         <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>387</v>
+        <v>137</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6351,7 +6257,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6363,7 +6269,7 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6372,7 +6278,7 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>391</v>
+        <v>134</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
@@ -6386,21 +6292,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6409,20 +6315,22 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>394</v>
+        <v>160</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6471,13 +6379,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6489,10 +6397,10 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>82</v>
@@ -6506,10 +6414,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6517,28 +6425,28 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>160</v>
+        <v>389</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>161</v>
+        <v>390</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>162</v>
+        <v>391</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6589,10 +6497,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>163</v>
+        <v>388</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>91</v>
@@ -6601,7 +6509,7 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6610,13 +6518,13 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>164</v>
+        <v>392</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -6624,24 +6532,24 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>136</v>
+        <v>395</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
@@ -6650,18 +6558,18 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>138</v>
+        <v>396</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6709,34 +6617,34 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>170</v>
+        <v>394</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>164</v>
+        <v>400</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -6744,14 +6652,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6764,13 +6672,13 @@
         <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>403</v>
@@ -6778,12 +6686,8 @@
       <c r="M42" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="N42" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -6807,13 +6711,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -6831,7 +6735,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6843,16 +6747,16 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>134</v>
+        <v>407</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -6866,10 +6770,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6880,7 +6784,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -6892,19 +6796,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>160</v>
+        <v>409</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -6953,13 +6857,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -6971,10 +6875,10 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
@@ -6983,489 +6887,11 @@
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="44" hidden="true">
-      <c r="A44" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="45" hidden="true">
-      <c r="A45" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="P45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="47" hidden="true">
-      <c r="A47" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="P47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP47" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP47">
+  <autoFilter ref="A1:AP43">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7475,7 +6901,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI46">
+  <conditionalFormatting sqref="A2:AI42">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$53</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2068" uniqueCount="486">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -746,6 +746,12 @@
   </si>
   <si>
     <t>outboundRelationship[typeCode=FLFS].target</t>
+  </si>
+  <si>
+    <t>1689: reference from EM - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (#63.02-.35 &gt; 63.52-3)</t>
+  </si>
+  <si>
+    <t>Pathology.EMOrderedTest.CPRSOrderIEN</t>
   </si>
   <si>
     <t>DiagnosticReport.status</t>
@@ -1092,10 +1098,10 @@
     <t>FiveWs.actor</t>
   </si>
   <si>
-    <t>1432: source value from ELECTRON MICROSCOPY - RELEASED BY (#63.02-.13)</t>
-  </si>
-  <si>
-    <t>Pathology.ElectronMicroscopy.ReleasedByStaffIEN</t>
+    <t>1685: reference from ELECTRON MICROSCOPY - RELEASING SITE (#63.02-.345)</t>
+  </si>
+  <si>
+    <t>Pathology.ElectronMicroscopy.ReleasingInstitutionIEN</t>
   </si>
   <si>
     <t>DiagnosticReport.resultsInterpreter</t>
@@ -1121,10 +1127,16 @@
     <t>OBR-32, PRT-8 (where this PRT-4-Participation = "PI")</t>
   </si>
   <si>
+    <t>1696: reference from EM - PATHOLOGIST (#63.02-.02)</t>
+  </si>
+  <si>
+    <t>Pathology.ElectronMicroscopy.PathologistStaffIEN</t>
+  </si>
+  <si>
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationElectronMicroscopySpecimen)
 </t>
   </si>
   <si>
@@ -1141,6 +1153,12 @@
   </si>
   <si>
     <t>SPM</t>
+  </si>
+  <si>
+    <t>1697: reference from EM - EM ACC # (#63.02-.06)</t>
+  </si>
+  <si>
+    <t>Pathology.ElectronMicroscopy.ElectronMicroscopyAccession</t>
   </si>
   <si>
     <t>DiagnosticReport.result</t>
@@ -1150,7 +1168,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationElectronMicroscopyObservation)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-lab)
 </t>
   </si>
   <si>
@@ -1170,9 +1188,6 @@
   </si>
   <si>
     <t>outboundRelationship[typeCode=COMP].target</t>
-  </si>
-  <si>
-    <t>++: reference</t>
   </si>
   <si>
     <t>DiagnosticReport.imagingStudy</t>
@@ -1340,6 +1355,207 @@
   </si>
   <si>
     <t>text (type=ED)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.contentType</t>
+  </si>
+  <si>
+    <t>Mime type of the content, with charset etc.</t>
+  </si>
+  <si>
+    <t>Identifies the type of the data in the attachment and allows a method to be chosen to interpret or render the data. Includes mime type parameters such as charset where appropriate.</t>
+  </si>
+  <si>
+    <t>Processors of the data need to be able to know how to interpret the data.</t>
+  </si>
+  <si>
+    <t>text/plain; charset=UTF-8, image/png</t>
+  </si>
+  <si>
+    <t>The mime type of an attachment. Any valid mime type is allowed.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/mimetypes|4.0.1</t>
+  </si>
+  <si>
+    <t>Attachment.contentType</t>
+  </si>
+  <si>
+    <t>ED.2+ED.3/RP.2+RP.3. Note conversion may be needed if old style values are being used</t>
+  </si>
+  <si>
+    <t>./mediaType, ./charset</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.language</t>
+  </si>
+  <si>
+    <t>Human language of the content (BCP-47)</t>
+  </si>
+  <si>
+    <t>The human language of the content. The value can be any valid value according to BCP 47.</t>
+  </si>
+  <si>
+    <t>Users need to be able to choose between the languages in a set of attachments.</t>
+  </si>
+  <si>
+    <t>en-AU</t>
+  </si>
+  <si>
+    <t>Attachment.language</t>
+  </si>
+  <si>
+    <t>./language</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base64Binary
+</t>
+  </si>
+  <si>
+    <t>Data inline, base64ed</t>
+  </si>
+  <si>
+    <t>The actual data of the attachment - a sequence of bytes, base64 encoded.</t>
+  </si>
+  <si>
+    <t>The base64-encoded data SHALL be expressed in the same character set as the base resource XML or JSON.</t>
+  </si>
+  <si>
+    <t>The data needs to able to be transmitted inline.</t>
+  </si>
+  <si>
+    <t>Attachment.data</t>
+  </si>
+  <si>
+    <t>ED.5</t>
+  </si>
+  <si>
+    <t>./data</t>
+  </si>
+  <si>
+    <t>1720: source value from EM - TIU REFERENCE DATE/TIME - EM &gt; TIU REFERENCE DATE/TIME - EM - TIU ENTRY POINTER - EM &gt; REPORT TEXT (#63.02-.16 &gt; 63.49-1 &gt; 8925-2)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url
+</t>
+  </si>
+  <si>
+    <t>Uri where the data can be found</t>
+  </si>
+  <si>
+    <t>A location where the data can be accessed.</t>
+  </si>
+  <si>
+    <t>If both data and url are provided, the url SHALL point to the same content as the data contains. Urls may be relative references or may reference transient locations such as a wrapping envelope using cid: though this has ramifications for using signatures. Relative URLs are interpreted relative to the service url, like a resource reference, rather than relative to the resource itself. If a URL is provided, it SHALL resolve to actual data.</t>
+  </si>
+  <si>
+    <t>The data needs to be transmitted by reference.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/logo-small.png</t>
+  </si>
+  <si>
+    <t>Attachment.url</t>
+  </si>
+  <si>
+    <t>RP.1+RP.2 - if they refer to a URL (see v2.6)</t>
+  </si>
+  <si>
+    <t>./reference/literal</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unsignedInt
+</t>
+  </si>
+  <si>
+    <t>Number of bytes of content (if url provided)</t>
+  </si>
+  <si>
+    <t>The number of bytes of data that make up this attachment (before base64 encoding, if that is done).</t>
+  </si>
+  <si>
+    <t>The number of bytes is redundant if the data is provided as a base64binary, but is useful if the data is provided as a url reference.</t>
+  </si>
+  <si>
+    <t>Representing the size allows applications to determine whether they should fetch the content automatically in advance, or refuse to fetch it at all.</t>
+  </si>
+  <si>
+    <t>Attachment.size</t>
+  </si>
+  <si>
+    <t>N/A (needs data type R3 proposal)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.hash</t>
+  </si>
+  <si>
+    <t>Hash of the data (sha-1, base64ed)</t>
+  </si>
+  <si>
+    <t>The calculated hash of the data using SHA-1. Represented using base64.</t>
+  </si>
+  <si>
+    <t>The hash is calculated on the data prior to base64 encoding, if the data is based64 encoded. The hash is not intended to support digital signatures. Where protection against malicious threats a digital signature should be considered, see [Provenance.signature](provenance-definitions.html#Provenance.signature) for mechanism to protect a resource with a digital signature.</t>
+  </si>
+  <si>
+    <t>Included so that applications can verify that the contents of a location have not changed due to technical failures (e.g., storage rot, transport glitch, incorrect version).</t>
+  </si>
+  <si>
+    <t>Attachment.hash</t>
+  </si>
+  <si>
+    <t>.integrityCheck[parent::ED/integrityCheckAlgorithm="SHA-1"]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.title</t>
+  </si>
+  <si>
+    <t>Label to display in place of the data</t>
+  </si>
+  <si>
+    <t>A label or set of text to display in place of the data.</t>
+  </si>
+  <si>
+    <t>Applications need a label to display to a human user in place of the actual data if the data cannot be rendered or perceived by the viewer.</t>
+  </si>
+  <si>
+    <t>Official Corporate Logo</t>
+  </si>
+  <si>
+    <t>Attachment.title</t>
+  </si>
+  <si>
+    <t>./title/data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.creation</t>
+  </si>
+  <si>
+    <t>Date attachment was first created</t>
+  </si>
+  <si>
+    <t>The date that the attachment was first created.</t>
+  </si>
+  <si>
+    <t>This is often tracked as an integrity issue for use of the attachment.</t>
+  </si>
+  <si>
+    <t>Attachment.creation</t>
   </si>
 </sst>
 </file>
@@ -1656,11 +1872,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP43"/>
+  <dimension ref="A1:AP53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.51953125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.37890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="43.5859375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -1698,7 +1914,7 @@
     <col min="38" max="38" width="171.66796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="121.93359375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="133.390625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="161.8203125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="61.08203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -4013,7 +4229,7 @@
         <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>82</v>
@@ -4110,18 +4326,18 @@
         <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4147,14 +4363,14 @@
         <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4183,7 +4399,7 @@
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4201,7 +4417,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>91</v>
@@ -4210,40 +4426,40 @@
         <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4265,13 +4481,13 @@
         <v>182</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4297,19 +4513,19 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
@@ -4319,7 +4535,7 @@
         <v>169</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4337,13 +4553,13 @@
         <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -4354,16 +4570,16 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4385,13 +4601,13 @@
         <v>182</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4402,7 +4618,7 @@
         <v>82</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>82</v>
@@ -4417,13 +4633,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -4441,7 +4657,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4459,13 +4675,13 @@
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -4476,14 +4692,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4505,13 +4721,13 @@
         <v>182</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4540,10 +4756,10 @@
         <v>187</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4561,7 +4777,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>91</v>
@@ -4576,16 +4792,16 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -4596,14 +4812,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4622,17 +4838,17 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4681,7 +4897,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4696,16 +4912,16 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -4716,14 +4932,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4742,19 +4958,19 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4803,7 +5019,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4818,16 +5034,16 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -4838,14 +5054,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4864,19 +5080,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -4913,7 +5129,7 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
@@ -4923,7 +5139,7 @@
         <v>169</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4932,22 +5148,22 @@
         <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -4958,16 +5174,16 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4986,19 +5202,19 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5047,7 +5263,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5056,40 +5272,40 @@
         <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5108,19 +5324,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5169,7 +5385,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5178,7 +5394,7 @@
         <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>103</v>
@@ -5187,31 +5403,31 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5230,19 +5446,19 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5291,7 +5507,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5306,34 +5522,34 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5343,7 +5559,7 @@
         <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -5352,19 +5568,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5413,7 +5629,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5428,30 +5644,30 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5465,7 +5681,7 @@
         <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
@@ -5474,19 +5690,19 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5535,7 +5751,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5553,31 +5769,31 @@
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5596,19 +5812,19 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5657,7 +5873,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5675,16 +5891,16 @@
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -5692,10 +5908,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5718,16 +5934,16 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5777,7 +5993,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5798,7 +6014,7 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
@@ -5812,14 +6028,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5838,17 +6054,17 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -5897,7 +6113,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5915,10 +6131,10 @@
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
@@ -5932,10 +6148,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6050,10 +6266,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6170,14 +6386,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6199,10 +6415,10 @@
         <v>137</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>140</v>
@@ -6257,7 +6473,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6292,10 +6508,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6321,16 +6537,16 @@
         <v>160</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6379,7 +6595,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6400,7 +6616,7 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>82</v>
@@ -6414,10 +6630,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6440,13 +6656,13 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6497,7 +6713,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>91</v>
@@ -6518,13 +6734,13 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -6532,14 +6748,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6561,14 +6777,14 @@
         <v>160</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6617,7 +6833,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6635,16 +6851,16 @@
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -6652,10 +6868,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6681,10 +6897,10 @@
         <v>182</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6711,13 +6927,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -6735,7 +6951,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6753,10 +6969,10 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -6770,10 +6986,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6796,19 +7012,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -6857,7 +7073,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6875,10 +7091,10 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
@@ -6887,11 +7103,1217 @@
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP44" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP46" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP49" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP43">
+  <autoFilter ref="A1:AP53">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6901,7 +8323,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI42">
+  <conditionalFormatting sqref="A2:AI52">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$70</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2567" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2720" uniqueCount="574">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -745,6 +745,12 @@
     <t>This allows tracing of authorization for the report and tracking whether proposals/recommendations were acted upon.</t>
   </si>
   <si>
+    <t>1689: reference from EM - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (63.02-.35 &gt; 63.52-3)</t>
+  </si>
+  <si>
+    <t>Pathology.EMOrderedTest.CPRSOrderIEN,Pathology.EMOrderedTest.CPRSOrderSID</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
   </si>
   <si>
@@ -827,6 +833,70 @@
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - WKLD CODE LAB SECTION &gt; WKLD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+  </si>
+  <si>
+    <t>Dim.LabChemTest.NationalVALabCodeIEN</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>DiagnosticReport.category:LaboratorySlice</t>
@@ -841,6 +911,9 @@
     &lt;code value="LAB"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>1419: fixed value = http://terminology.hl7.org/CodeSystem/v2-0074#LAB</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -898,29 +971,7 @@
     <t>DiagnosticReport.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
+    <t>1420: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC (60-64 &gt; 64-25 &gt; 95.3)</t>
   </si>
   <si>
     <t>DiagnosticReport.code.coding.id</t>
@@ -950,7 +1001,7 @@
     <t>Coding.system</t>
   </si>
   <si>
-    <t>1814-1: fixed value = http://loinc.org</t>
+    <t>1420-2: fixed value = http://loinc.org</t>
   </si>
   <si>
     <t>C*E.3</t>
@@ -995,7 +1046,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1814: source value from EM - TIU REFERENCE DATE/TIME - EM &gt; TIU REFERENCE DATE/TIME - EM - TIU ENTRY POINTER - EM &gt; TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - CODING SYSTEM &gt; CODING SYSTEM - CODE &gt; CODE - CODE (63.02-.16 &gt; 63.49-1 &gt; 8925-.01 &gt; 8925.1-1501 &gt; 8926.1-2 &gt; 8926.12-.02 &gt; 8926.121-.01)</t>
+    <t>1420-1: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - CODE (60-64 &gt; 64-25 &gt; 95.3-.01)</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1017,6 +1068,9 @@
   </si>
   <si>
     <t>Coding.display</t>
+  </si>
+  <si>
+    <t>1420-3: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - COMPONENT (60-64 &gt; 64-25 &gt; 95.3-1)</t>
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
@@ -1056,28 +1110,10 @@
     <t>DiagnosticReport.code.text</t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>1812: source value from EM - TIU REFERENCE DATE/TIME - EM &gt; TIU REFERENCE DATE/TIME - EM - TIU ENTRY POINTER - EM &gt; TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - NAME (63.02-.16 &gt; 63.49-1 &gt; 8925-.01 &gt; 8925.1-.01)</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
+    <t>1661: source value from LABORATORY TEST - NAME (60-.01)</t>
+  </si>
+  <si>
+    <t>Dim.LabChemTest.LabChemTestName</t>
   </si>
   <si>
     <t>DiagnosticReport.subject</t>
@@ -1100,6 +1136,12 @@
     <t>SHALL know the subject context.</t>
   </si>
   <si>
+    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1379,7 +1421,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-lab)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationObservation)
 </t>
   </si>
   <si>
@@ -1393,6 +1435,9 @@
   </si>
   <si>
     <t>Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>
+  </si>
+  <si>
+    <t>1437: reference from See mapping for Lab Observation</t>
   </si>
   <si>
     <t>OBXs</t>
@@ -2083,7 +2128,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP66"/>
+  <dimension ref="A1:AP70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.51953125" customWidth="true" bestFit="true"/>
@@ -2121,7 +2166,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="176.40234375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="171.66796875" customWidth="true" bestFit="true"/>
@@ -4440,7 +4485,7 @@
         <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>82</v>
@@ -4525,19 +4570,19 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>82</v>
+        <v>234</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4545,10 +4590,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4574,14 +4619,14 @@
         <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4610,7 +4655,7 @@
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4628,7 +4673,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>91</v>
@@ -4637,40 +4682,40 @@
         <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4692,13 +4737,13 @@
         <v>182</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4724,19 +4769,19 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
@@ -4746,7 +4791,7 @@
         <v>169</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4770,56 +4815,52 @@
         <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>251</v>
+        <v>161</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4829,7 +4870,7 @@
         <v>82</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>82</v>
@@ -4844,13 +4885,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -4868,19 +4909,19 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>249</v>
+        <v>163</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -4892,13 +4933,13 @@
         <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>260</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -4910,35 +4951,35 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>265</v>
+        <v>136</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>266</v>
+        <v>138</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>267</v>
+        <v>166</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4949,7 +4990,7 @@
         <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>82</v>
@@ -4964,69 +5005,69 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>264</v>
+        <v>170</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>272</v>
+        <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>275</v>
+        <v>164</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5037,7 +5078,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -5046,19 +5087,23 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5106,19 +5151,19 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>163</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -5130,10 +5175,10 @@
         <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>82</v>
+        <v>272</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>164</v>
+        <v>273</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5141,44 +5186,46 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>138</v>
+        <v>275</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>166</v>
+        <v>276</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5214,46 +5261,46 @@
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>170</v>
+        <v>279</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>164</v>
+        <v>283</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5261,24 +5308,26 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
@@ -5287,20 +5336,18 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>280</v>
+        <v>182</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5309,7 +5356,7 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>82</v>
@@ -5324,13 +5371,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5348,7 +5395,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5363,7 +5410,7 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
@@ -5372,13 +5419,13 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -5390,34 +5437,36 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>161</v>
+        <v>290</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5427,7 +5476,7 @@
         <v>82</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>82</v>
@@ -5442,13 +5491,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5466,10 +5515,10 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>163</v>
+        <v>288</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>91</v>
@@ -5478,44 +5527,44 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>164</v>
+        <v>299</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5527,17 +5576,15 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5574,31 +5621,31 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5621,46 +5668,44 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>291</v>
+        <v>138</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>292</v>
+        <v>166</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5669,7 +5714,7 @@
         <v>82</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>82</v>
@@ -5696,34 +5741,34 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>296</v>
+        <v>170</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>82</v>
@@ -5732,10 +5777,10 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>299</v>
+        <v>164</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5743,10 +5788,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5757,10 +5802,10 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -5769,18 +5814,20 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5828,13 +5875,13 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
@@ -5843,19 +5890,19 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>305</v>
+        <v>272</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>306</v>
+        <v>273</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5863,10 +5910,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5880,27 +5927,25 @@
         <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>308</v>
+        <v>161</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>309</v>
+        <v>162</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>310</v>
-      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -5948,7 +5993,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>311</v>
+        <v>163</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5960,10 +6005,10 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
@@ -5972,10 +6017,10 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>314</v>
+        <v>164</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -5983,21 +6028,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -6006,21 +6051,21 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>316</v>
+        <v>138</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6056,31 +6101,31 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>319</v>
+        <v>170</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6092,10 +6137,10 @@
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>320</v>
+        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>321</v>
+        <v>164</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -6103,10 +6148,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6120,7 +6165,7 @@
         <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -6129,19 +6174,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>323</v>
+        <v>105</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6151,7 +6196,7 @@
         <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>82</v>
@@ -6190,7 +6235,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6205,7 +6250,7 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
@@ -6214,10 +6259,10 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6225,10 +6270,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6242,7 +6287,7 @@
         <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6254,17 +6299,15 @@
         <v>160</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6312,7 +6355,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6327,7 +6370,7 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>337</v>
+        <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>82</v>
@@ -6336,10 +6379,10 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6347,18 +6390,18 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>91</v>
@@ -6373,17 +6416,17 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>342</v>
+        <v>111</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6432,7 +6475,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6447,34 +6490,34 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6484,7 +6527,7 @@
         <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6493,19 +6536,17 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>352</v>
+        <v>160</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6554,7 +6595,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6569,34 +6610,34 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6606,7 +6647,7 @@
         <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -6615,19 +6656,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6664,17 +6705,19 @@
         <v>82</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AC38" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6683,7 +6726,7 @@
         <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>103</v>
@@ -6695,30 +6738,28 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6737,19 +6778,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>376</v>
+        <v>160</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>364</v>
+        <v>275</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>366</v>
+        <v>277</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>367</v>
+        <v>278</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6798,7 +6839,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>361</v>
+        <v>279</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6807,44 +6848,44 @@
         <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>377</v>
+        <v>350</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>378</v>
+        <v>351</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>371</v>
+        <v>282</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>372</v>
+        <v>283</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>379</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>379</v>
+        <v>352</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>380</v>
+        <v>353</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>91</v>
@@ -6859,19 +6900,17 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>381</v>
+        <v>354</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6920,7 +6959,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>379</v>
+        <v>352</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6929,50 +6968,50 @@
         <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>387</v>
+        <v>358</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>389</v>
+        <v>361</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>390</v>
+        <v>362</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>391</v>
+        <v>363</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>393</v>
+        <v>365</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
@@ -6981,19 +7020,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>394</v>
+        <v>366</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>395</v>
+        <v>367</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>396</v>
+        <v>368</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>397</v>
+        <v>369</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7030,23 +7069,25 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
@@ -7061,30 +7102,28 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>399</v>
+        <v>371</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>400</v>
+        <v>372</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>401</v>
+        <v>373</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>402</v>
+        <v>374</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>403</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7103,19 +7142,19 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>405</v>
+        <v>377</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7152,63 +7191,61 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>406</v>
+        <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7227,19 +7264,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7288,56 +7325,56 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>413</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>413</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>92</v>
@@ -7349,19 +7386,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7410,49 +7447,49 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>413</v>
+        <v>393</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7468,22 +7505,22 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7520,19 +7557,17 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7547,41 +7582,43 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>348</v>
+        <v>415</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="D46" t="s" s="2">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>92</v>
@@ -7590,22 +7627,22 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>434</v>
+        <v>409</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>436</v>
+        <v>411</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>437</v>
+        <v>412</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7654,7 +7691,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>431</v>
+        <v>406</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7669,64 +7706,68 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="D47" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>442</v>
+        <v>409</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -7774,7 +7815,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>440</v>
+        <v>406</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7789,34 +7830,34 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>445</v>
+        <v>415</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7826,7 +7867,7 @@
         <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
@@ -7835,17 +7876,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>451</v>
+        <v>412</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7894,7 +7937,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7909,30 +7952,30 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>452</v>
+        <v>435</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7943,10 +7986,10 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>82</v>
@@ -7955,16 +7998,20 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>160</v>
+        <v>437</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>161</v>
+        <v>438</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8012,34 +8059,34 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>163</v>
+        <v>436</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>164</v>
+        <v>362</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8047,14 +8094,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>136</v>
+        <v>446</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8064,7 +8111,7 @@
         <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
@@ -8073,18 +8120,20 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>137</v>
+        <v>447</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>138</v>
+        <v>448</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>166</v>
+        <v>449</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8132,7 +8181,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>170</v>
+        <v>445</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8144,10 +8193,10 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
@@ -8156,10 +8205,10 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>164</v>
+        <v>454</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8174,7 +8223,7 @@
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8187,13 +8236,13 @@
         <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>137</v>
+        <v>456</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>457</v>
@@ -8202,11 +8251,9 @@
         <v>458</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8254,7 +8301,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8266,7 +8313,7 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8281,7 +8328,7 @@
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>134</v>
+        <v>460</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8289,21 +8336,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>82</v>
+        <v>462</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8312,22 +8359,20 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>160</v>
+        <v>463</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8376,13 +8421,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8400,10 +8445,10 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8411,10 +8456,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8422,28 +8467,28 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>467</v>
+        <v>160</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>468</v>
+        <v>161</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>469</v>
+        <v>162</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8494,10 +8539,10 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>466</v>
+        <v>163</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>91</v>
@@ -8506,10 +8551,10 @@
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
@@ -8521,7 +8566,7 @@
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>471</v>
+        <v>164</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8529,24 +8574,24 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>473</v>
+        <v>136</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>82</v>
@@ -8555,18 +8600,18 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>474</v>
+        <v>138</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>476</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8614,22 +8659,22 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>472</v>
+        <v>170</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
@@ -8638,10 +8683,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>478</v>
+        <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>479</v>
+        <v>164</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8649,14 +8694,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>82</v>
+        <v>471</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8669,22 +8714,26 @@
         <v>82</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8708,13 +8757,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8732,7 +8781,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8744,7 +8793,7 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8756,10 +8805,10 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>478</v>
+        <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>485</v>
+        <v>134</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8767,10 +8816,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8781,7 +8830,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8793,19 +8842,19 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>487</v>
+        <v>160</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8854,13 +8903,13 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
@@ -8878,10 +8927,10 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>478</v>
+        <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -8889,10 +8938,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8900,28 +8949,28 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>160</v>
+        <v>482</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>161</v>
+        <v>483</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>162</v>
+        <v>484</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8972,10 +9021,10 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>163</v>
+        <v>481</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>91</v>
@@ -8984,10 +9033,10 @@
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
@@ -8999,7 +9048,7 @@
         <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>164</v>
+        <v>486</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9007,24 +9056,24 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>136</v>
+        <v>488</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -9033,18 +9082,18 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>138</v>
+        <v>489</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9080,34 +9129,34 @@
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>170</v>
+        <v>487</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
@@ -9116,10 +9165,10 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>82</v>
+        <v>493</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>164</v>
+        <v>494</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -9141,7 +9190,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9150,10 +9199,10 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>496</v>
@@ -9162,9 +9211,7 @@
         <v>497</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>498</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9176,26 +9223,26 @@
         <v>82</v>
       </c>
       <c r="T59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="U59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>501</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9212,13 +9259,13 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
@@ -9236,10 +9283,10 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9247,10 +9294,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9261,7 +9308,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9270,20 +9317,22 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>111</v>
+        <v>502</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="O60" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9296,7 +9345,7 @@
         <v>82</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>82</v>
@@ -9308,13 +9357,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9332,13 +9381,13 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
@@ -9356,10 +9405,10 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>82</v>
+        <v>493</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9367,10 +9416,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9384,7 +9433,7 @@
         <v>91</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>82</v>
@@ -9393,20 +9442,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>513</v>
+        <v>160</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>514</v>
+        <v>161</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9454,7 +9499,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>518</v>
+        <v>163</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9466,10 +9511,10 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>519</v>
+        <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
@@ -9478,10 +9523,10 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>520</v>
+        <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>521</v>
+        <v>164</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -9489,21 +9534,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9512,23 +9557,21 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>523</v>
+        <v>137</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>524</v>
+        <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>525</v>
+        <v>166</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9540,7 +9583,7 @@
         <v>82</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>82</v>
@@ -9564,31 +9607,31 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>529</v>
+        <v>170</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9600,10 +9643,10 @@
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>531</v>
+        <v>164</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>
@@ -9611,10 +9654,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>532</v>
+        <v>510</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>532</v>
+        <v>510</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9637,19 +9680,17 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>533</v>
+        <v>111</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>534</v>
+        <v>511</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>536</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>537</v>
+        <v>513</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9662,7 +9703,7 @@
         <v>82</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>82</v>
+        <v>514</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>82</v>
@@ -9674,13 +9715,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>82</v>
+        <v>515</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9698,7 +9739,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9722,10 +9763,10 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>82</v>
+        <v>518</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>539</v>
+        <v>519</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
@@ -9733,10 +9774,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9759,19 +9800,17 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>513</v>
+        <v>111</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>543</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9784,7 +9823,7 @@
         <v>82</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>82</v>
+        <v>524</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>82</v>
@@ -9796,13 +9835,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9820,7 +9859,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9847,7 +9886,7 @@
         <v>82</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>546</v>
+        <v>526</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>82</v>
@@ -9855,10 +9894,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>547</v>
+        <v>527</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>547</v>
+        <v>527</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9872,26 +9911,28 @@
         <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>160</v>
+        <v>528</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>548</v>
+        <v>529</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>531</v>
+      </c>
       <c r="O65" t="s" s="2">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9904,7 +9945,7 @@
         <v>82</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>551</v>
+        <v>82</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>82</v>
@@ -9940,7 +9981,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>552</v>
+        <v>533</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9955,7 +9996,7 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>82</v>
@@ -9964,10 +10005,10 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>82</v>
@@ -9975,10 +10016,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10001,17 +10042,19 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>376</v>
+        <v>538</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>540</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>557</v>
+        <v>542</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10024,7 +10067,7 @@
         <v>82</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>82</v>
+        <v>543</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>82</v>
@@ -10060,7 +10103,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10084,17 +10127,501 @@
         <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>82</v>
+        <v>545</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="AP66" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP66">
+  <autoFilter ref="A1:AP70">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10104,7 +10631,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI65">
+  <conditionalFormatting sqref="A2:AI69">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2720" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2720" uniqueCount="573">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -729,7 +729,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest)
 </t>
   </si>
   <si>
@@ -1123,7 +1123,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1331,7 +1331,7 @@
     <t>va-by</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>
@@ -1347,7 +1347,7 @@
     <t>va-at</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization)
 </t>
   </si>
   <si>
@@ -1362,10 +1362,6 @@
   <si>
     <t>Analyzed by
 Reported by</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam)
-</t>
   </si>
   <si>
     <t>Primary result interpreter</t>
@@ -7876,16 +7872,16 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>412</v>
@@ -7952,16 +7948,16 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>413</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>415</v>
@@ -7972,10 +7968,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7998,19 +7994,19 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8059,7 +8055,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8074,16 +8070,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>362</v>
@@ -8094,14 +8090,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8120,19 +8116,19 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8181,7 +8177,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8196,19 +8192,19 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8216,10 +8212,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8242,16 +8238,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8301,7 +8297,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8328,7 +8324,7 @@
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8336,14 +8332,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8362,17 +8358,17 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8421,7 +8417,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8445,10 +8441,10 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8456,10 +8452,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8574,10 +8570,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8694,14 +8690,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8723,10 +8719,10 @@
         <v>137</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>140</v>
@@ -8781,7 +8777,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8816,10 +8812,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8845,16 +8841,16 @@
         <v>160</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8903,7 +8899,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8930,7 +8926,7 @@
         <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -8938,10 +8934,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8964,13 +8960,13 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9021,7 +9017,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>91</v>
@@ -9036,19 +9032,19 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9056,14 +9052,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9085,14 +9081,14 @@
         <v>160</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9141,7 +9137,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9156,19 +9152,19 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AL58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -9176,10 +9172,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9205,10 +9201,10 @@
         <v>182</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9238,11 +9234,11 @@
         <v>256</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9259,7 +9255,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9283,10 +9279,10 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9294,10 +9290,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9320,19 +9316,19 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9381,7 +9377,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9405,10 +9401,10 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9416,10 +9412,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9534,10 +9530,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9654,10 +9650,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9683,14 +9679,14 @@
         <v>111</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9703,7 +9699,7 @@
         <v>82</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>82</v>
@@ -9718,28 +9714,28 @@
         <v>176</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="Z63" t="s" s="2">
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9763,10 +9759,10 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
@@ -9774,10 +9770,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9803,14 +9799,14 @@
         <v>111</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9823,7 +9819,7 @@
         <v>82</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>82</v>
@@ -9859,7 +9855,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9886,7 +9882,7 @@
         <v>82</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>82</v>
@@ -9894,10 +9890,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9920,19 +9916,19 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9981,7 +9977,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9996,19 +9992,19 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="AL65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>82</v>
@@ -10016,10 +10012,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10042,19 +10038,19 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10067,43 +10063,43 @@
         <v>82</v>
       </c>
       <c r="T66" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10127,10 +10123,10 @@
         <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AO66" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>82</v>
@@ -10138,10 +10134,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10164,19 +10160,19 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10225,7 +10221,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10252,7 +10248,7 @@
         <v>82</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>82</v>
@@ -10260,10 +10256,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10286,19 +10282,19 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10347,7 +10343,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10374,7 +10370,7 @@
         <v>82</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>82</v>
@@ -10382,10 +10378,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10411,14 +10407,14 @@
         <v>160</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10431,43 +10427,43 @@
         <v>82</v>
       </c>
       <c r="T69" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10494,7 +10490,7 @@
         <v>82</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>82</v>
@@ -10502,10 +10498,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10531,14 +10527,14 @@
         <v>390</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10587,7 +10583,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10614,7 +10610,7 @@
         <v>82</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1762,7 +1762,7 @@
     <t>The calculated hash of the data using SHA-1. Represented using base64.</t>
   </si>
   <si>
-    <t>The hash is calculated on the data prior to base64 encoding, if the data is based64 encoded. The hash is not intended to support digital signatures. Where protection against malicious threats a digital signature should be considered, see [Provenance.signature](provenance-definitions.html#Provenance.signature) for mechanism to protect a resource with a digital signature.</t>
+    <t>The hash is calculated on the data prior to base64 encoding, if the data is based64 encoded. The hash is not intended to support digital signatures. Where protection against malicious threats a digital signature should be considered, see [Provenance.signature](http://hl7.org/fhir/R4/provenance-definitions.html#Provenance.signature) for mechanism to protect a resource with a digital signature.</t>
   </si>
   <si>
     <t>Included so that applications can verify that the contents of a location have not changed due to technical failures (e.g., storage rot, transport glitch, incorrect version).</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -772,7 +772,7 @@
     <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFDiagnosticReportLabStatus</t>
+    <t>http://va.gov/fhir/ValueSet/DiagnosticReportLabStatus</t>
   </si>
   <si>
     <t>us-core-8

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -947,7 +947,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-lab-codes</t>
   </si>
   <si>
-    <t>1813: fixed value = http://loinc.org#50668-3 Microscopic observation in Specimen by Electron microscopy Narrative</t>
+    <t>1813: fixed value = http://loinc.org#50668-3 "Microscopic observation in Specimen by Electron microscopy Narrative"</t>
   </si>
   <si>
     <t>Event.code</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1145,7 +1145,8 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn</t>
+    <t>demographics.lrdfn
+accession.collected</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -2171,7 +2171,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="176.40234375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="171.66796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="121.93359375" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1145,8 +1145,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn
-accession.collected</t>
+    <t>Patient.PatientExtension.VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1145,7 +1145,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>Patient.PatientExtension.VeteranLrdfn</t>
+    <t>Patient.Extension[PatientExtension].VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file EM (63.02) to us-core-diagnosticreport-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file EM (63.02) to us-core-diagnosticreport-lab.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2790" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2790" uniqueCount="576">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1317,6 +1317,10 @@
   </si>
   <si>
     <t>Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -7692,7 +7696,7 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>260</v>
+        <v>415</v>
       </c>
       <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
@@ -7726,27 +7730,27 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>408</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>409</v>
@@ -7768,7 +7772,7 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>411</v>
@@ -7844,36 +7848,36 @@
         <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>408</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>409</v>
@@ -7895,7 +7899,7 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>411</v>
@@ -7971,37 +7975,37 @@
         <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8020,16 +8024,16 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>414</v>
@@ -8081,7 +8085,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8096,33 +8100,33 @@
         <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8145,19 +8149,19 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8206,7 +8210,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8221,10 +8225,10 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>83</v>
@@ -8233,7 +8237,7 @@
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>364</v>
@@ -8244,14 +8248,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8270,19 +8274,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8331,7 +8335,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8346,7 +8350,7 @@
         <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>83</v>
@@ -8358,10 +8362,10 @@
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -8369,10 +8373,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8395,16 +8399,16 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8454,7 +8458,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8484,7 +8488,7 @@
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>83</v>
@@ -8492,14 +8496,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8518,17 +8522,17 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8577,7 +8581,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8604,10 +8608,10 @@
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>83</v>
@@ -8615,10 +8619,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8736,10 +8740,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8859,14 +8863,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8888,10 +8892,10 @@
         <v>138</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>141</v>
@@ -8946,7 +8950,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8984,10 +8988,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9013,16 +9017,16 @@
         <v>161</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -9071,7 +9075,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9101,7 +9105,7 @@
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>83</v>
@@ -9109,10 +9113,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9135,13 +9139,13 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9192,7 +9196,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>92</v>
@@ -9207,7 +9211,7 @@
         <v>104</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>83</v>
@@ -9222,7 +9226,7 @@
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -9230,14 +9234,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9259,14 +9263,14 @@
         <v>161</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9315,7 +9319,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9330,7 +9334,7 @@
         <v>104</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>83</v>
@@ -9342,10 +9346,10 @@
         <v>83</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -9353,10 +9357,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9382,10 +9386,10 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9415,10 +9419,10 @@
         <v>257</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -9436,7 +9440,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9463,10 +9467,10 @@
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>83</v>
@@ -9474,10 +9478,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9500,19 +9504,19 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9561,7 +9565,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9588,10 +9592,10 @@
         <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>83</v>
@@ -9599,10 +9603,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9720,10 +9724,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9843,10 +9847,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9872,14 +9876,14 @@
         <v>112</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9892,7 +9896,7 @@
         <v>83</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>83</v>
@@ -9907,10 +9911,10 @@
         <v>177</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -9928,7 +9932,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9955,10 +9959,10 @@
         <v>83</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>83</v>
@@ -9966,10 +9970,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9995,14 +9999,14 @@
         <v>112</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10015,7 +10019,7 @@
         <v>83</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>83</v>
@@ -10051,7 +10055,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10081,7 +10085,7 @@
         <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>
@@ -10089,10 +10093,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10115,19 +10119,19 @@
         <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10176,7 +10180,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10191,7 +10195,7 @@
         <v>104</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>83</v>
@@ -10203,10 +10207,10 @@
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>83</v>
@@ -10214,10 +10218,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10240,19 +10244,19 @@
         <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10265,7 +10269,7 @@
         <v>83</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>83</v>
@@ -10301,7 +10305,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10328,10 +10332,10 @@
         <v>83</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>83</v>
@@ -10339,10 +10343,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10365,19 +10369,19 @@
         <v>93</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10426,7 +10430,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10456,7 +10460,7 @@
         <v>83</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>83</v>
@@ -10464,10 +10468,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10490,19 +10494,19 @@
         <v>93</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10551,7 +10555,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10581,7 +10585,7 @@
         <v>83</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>83</v>
@@ -10589,10 +10593,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10618,14 +10622,14 @@
         <v>161</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10638,7 +10642,7 @@
         <v>83</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>83</v>
@@ -10674,7 +10678,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10704,7 +10708,7 @@
         <v>83</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>83</v>
@@ -10712,10 +10716,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10741,14 +10745,14 @@
         <v>392</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10797,7 +10801,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10827,7 +10831,7 @@
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -669,7 +669,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1604: source value from EM - ORDERED TEST &gt; ORDERED TEST - IEN (63.02-.35 &gt; 63.52-.001)</t>
+    <t>1604: source value based on EM - ORDERED TEST &gt; ORDERED TEST - IEN (63.02-.35 &gt; 63.52-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -748,7 +748,7 @@
     <t>This allows tracing of authorization for the report and tracking whether proposals/recommendations were acted upon.</t>
   </si>
   <si>
-    <t>1689: reference from EM - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (63.02-.35 &gt; 63.52-3)</t>
+    <t>1689: reference based on EM - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (63.02-.35 &gt; 63.52-3)</t>
   </si>
   <si>
     <t>Pathology.EMOrderedTest.CPRSOrderIEN,Pathology.EMOrderedTest.CPRSOrderSID</t>
@@ -890,7 +890,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - WKLD CODE LAB SECTION &gt; WKLD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+    <t>1662: source value based on LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - WKLD CODE LAB SECTION &gt; WKLD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
   </si>
   <si>
     <t>Dim.LabChemTest.NationalVALabCodeIEN</t>
@@ -974,7 +974,7 @@
     <t>DiagnosticReport.code.coding</t>
   </si>
   <si>
-    <t>1420: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC (60-64 &gt; 64-25 &gt; 95.3)</t>
+    <t>1420: source value based on LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC (60-64 &gt; 64-25 &gt; 95.3)</t>
   </si>
   <si>
     <t>DiagnosticReport.code.coding.id</t>
@@ -1049,7 +1049,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1420-1: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - CODE (60-64 &gt; 64-25 &gt; 95.3-.01)</t>
+    <t>1420-1: source value based on LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - CODE (60-64 &gt; 64-25 &gt; 95.3-.01)</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1073,7 +1073,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1420-3: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - COMPONENT (60-64 &gt; 64-25 &gt; 95.3-1)</t>
+    <t>1420-3: source value based on LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - COMPONENT (60-64 &gt; 64-25 &gt; 95.3-1)</t>
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
@@ -1113,7 +1113,7 @@
     <t>DiagnosticReport.code.text</t>
   </si>
   <si>
-    <t>1661: source value from LABORATORY TEST - NAME (60-.01)</t>
+    <t>1661: source value based on LABORATORY TEST - NAME (60-.01)</t>
   </si>
   <si>
     <t>Dim.LabChemTest.LabChemTestName</t>
@@ -1139,7 +1139,7 @@
     <t>SHALL know the subject context.</t>
   </si>
   <si>
-    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
+    <t>1421: reference based on PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
@@ -1248,7 +1248,7 @@
 </t>
   </si>
   <si>
-    <t>1422: source value from EM - DATE/TIME SPECIMEN TAKEN (63.02-.01)</t>
+    <t>1422: source value based on EM - DATE/TIME SPECIMEN TAKEN (63.02-.01)</t>
   </si>
   <si>
     <t>Pathology.ElectronMicroscopy.SpecimenTakenDateTime,Pathology.EMComment.SpecimenTakenDateTime,Pathology.EMDelayedComment.SpecimenTakenDateTime,Pathology.EMDiagnosis.SpecimenTakenDateTime,Pathology.EMGrossDescription.SpecimenTakenDateTime,Pathology.EMMicroscopicExam.SpecimenTakenDateTime,Pathology.EMOperativeFinding.SpecimenTakenDateTime,Pathology.EMOrderedTest.SpecimenTakenDateTime,Pathology.EMOrganTissueDisease.SpecimenTakenDateTime,Pathology.EMOrganTissueEtiology.SpecimenTakenDateTime,Pathology.EMOrganTissueFunction.SpecimenTakenDateTime,Pathology.EMOrganTissueMorphology.SpecimenTakenDateTime,Pathology.EMOrganTissueProcedure.SpecimenTakenDateTime,Pathology.EMPostOpDiagnosis.SpecimenTakenDateTime,Pathology.EMPreOpDiagnosis.SpecimenTakenDateTime,Pathology.EMSpecimen.SpecimenTakenDateTime,Pathology.EMSpecimenEPON.SpecimenTakenDateTime,Pathology.EMSpecimenEPONProcedure.SpecimenTakenDateTime,Pathology.EMSupplement.SpecimenTakenDateTime,Pathology.EMSupplementDescript.SpecimenTakenDateTime,Pathology.EMTIUReference.SpecimenTakenDateTime</t>
@@ -1281,7 +1281,7 @@
 </t>
   </si>
   <si>
-    <t>1427: source value from EM - DATE REPORT COMPLETED (63.02-.03)</t>
+    <t>1427: source value based on EM - DATE REPORT COMPLETED (63.02-.03)</t>
   </si>
   <si>
     <t>Pathology.ElectronMicroscopy.ReportCompleteDateTime</t>
@@ -1345,7 +1345,7 @@
 </t>
   </si>
   <si>
-    <t>1432: reference from EM - RELEASED BY (63.02-.13)</t>
+    <t>1432: reference based on EM - RELEASED BY (63.02-.13)</t>
   </si>
   <si>
     <t>Pathology.ElectronMicroscopy.ReleasedByStaffIEN,Pathology.ElectronMicroscopy.ReleasedByStaffSID</t>
@@ -1361,7 +1361,7 @@
 </t>
   </si>
   <si>
-    <t>1685: reference from EM - RELEASING SITE (63.02-.345)</t>
+    <t>1685: reference based on EM - RELEASING SITE (63.02-.345)</t>
   </si>
   <si>
     <t>Pathology.ElectronMicroscopy.ReleasingInstitutionIEN,Pathology.ElectronMicroscopy.ReleasingInstitutionSID</t>
@@ -1383,7 +1383,7 @@
     <t>Might not be the same entity that takes responsibility for the clinical report.</t>
   </si>
   <si>
-    <t>1696: reference from EM - PATHOLOGIST (63.02-.02)</t>
+    <t>1696: reference based on EM - PATHOLOGIST (63.02-.02)</t>
   </si>
   <si>
     <t>Pathology.ElectronMicroscopy.PathologistStaffIEN,Pathology.ElectronMicroscopy.PathologistStaffSID</t>
@@ -1411,7 +1411,7 @@
     <t>Need to be able to report information about the collected specimens on which the report is based.</t>
   </si>
   <si>
-    <t>1697: reference from EM - EM ACC # (63.02-.06)</t>
+    <t>1697: reference based on EM - EM ACC # (63.02-.06)</t>
   </si>
   <si>
     <t>Pathology.ElectronMicroscopy.ElectronMicroscopyAccession</t>
@@ -1443,7 +1443,7 @@
     <t>Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>
   </si>
   <si>
-    <t>1437: reference from See mapping for Lab Observation</t>
+    <t>1437: reference based on See mapping for Lab Observation</t>
   </si>
   <si>
     <t>OBXs</t>
@@ -1548,7 +1548,7 @@
     <t>Reference to the image source.</t>
   </si>
   <si>
-    <t>1438: reference from EM - IMAGE (63.02-2005)</t>
+    <t>1438: reference based on EM - IMAGE (63.02-2005)</t>
   </si>
   <si>
     <t>.value.reference</t>
@@ -1570,7 +1570,7 @@
     <t>Need to be able to provide a conclusion that is not lost among the basic result data.</t>
   </si>
   <si>
-    <t>1441: source value from EM - EM DIAGNOSIS (63.02-1.4)</t>
+    <t>1441: source value based on EM - EM DIAGNOSIS (63.02-1.4)</t>
   </si>
   <si>
     <t>OBX</t>
@@ -1698,7 +1698,7 @@
     <t>Attachment.data</t>
   </si>
   <si>
-    <t>1720: source value from EM - TIU REFERENCE DATE/TIME - EM &gt; TIU REFERENCE DATE/TIME - EM - TIU ENTRY POINTER - EM &gt; TIU DOCUMENT - REPORT TEXT (63.02-.16 &gt; 63.49-1 &gt; 8925-2)</t>
+    <t>1720: source value based on EM - TIU REFERENCE DATE/TIME - EM &gt; TIU REFERENCE DATE/TIME - EM - TIU ENTRY POINTER - EM &gt; TIU DOCUMENT - REPORT TEXT (63.02-.16 &gt; 63.49-1 &gt; 8925-2)</t>
   </si>
   <si>
     <t>ED.5</t>
@@ -2172,7 +2172,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="176.40234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="180.49609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LabObservationElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
